--- a/target/classes/com/mycompany/ocxrst/BASES/METODOPAGO.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/METODOPAGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733DDEB7-C020-434F-8829-CCFD33EB006E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCE8E62-94C9-4DEE-ABEF-3EFD6AF7149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{990EDD03-0934-488A-A009-C4014A91B927}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{990EDD03-0934-488A-A009-C4014A91B927}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>METODO DE PAGO</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>PPD (pago por partes)</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -423,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9DEEE3-EBB6-4D91-A09A-DFF350C26CCA}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.36328125" bestFit="1" customWidth="1"/>
@@ -436,11 +439,16 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
